--- a/StructureDefinition-fragestellung-tumorkonferenz-freitext.xlsx
+++ b/StructureDefinition-fragestellung-tumorkonferenz-freitext.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-29T08:55:06+02:00</t>
+    <t>2025-04-29T14:54:46+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-fragestellung-tumorkonferenz-freitext.xlsx
+++ b/StructureDefinition-fragestellung-tumorkonferenz-freitext.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-29T14:54:46+02:00</t>
+    <t>2025-04-29T15:11:56+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-fragestellung-tumorkonferenz-freitext.xlsx
+++ b/StructureDefinition-fragestellung-tumorkonferenz-freitext.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-29T15:11:56+02:00</t>
+    <t>2025-04-29T15:45:38+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
